--- a/data/output_marked.xlsx
+++ b/data/output_marked.xlsx
@@ -130,6 +130,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>AI_System</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>工资必须大于0，当前为0。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -460,18 +475,17 @@
           <t>102</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>工资必须大于 0</t>
-        </is>
+      <c r="C3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/data/output_marked.xlsx
+++ b/data/output_marked.xlsx
@@ -25,18 +25,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,9 +45,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -128,21 +121,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>AI_System</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0" shapeId="0">
-      <text>
-        <t>工资必须大于0，当前为0。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -470,7 +448,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>102</t>
         </is>
@@ -486,6 +464,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/data/output_marked.xlsx
+++ b/data/output_marked.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,21 +16,48 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Noto Sans JP"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -45,11 +72,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -123,10 +153,30 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>AI_System</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>[MOCK] 部门 [xxx] 非法，不在许可名单内</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>[MOCK] 工资必须大于 0</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +214,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,6 +248,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -232,9 +283,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -412,13 +464,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>员工ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -428,14 +480,24 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>工资</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>入职日期</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>101</t>
+    <row r="2" ht="15.6" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>1001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -443,14 +505,24 @@
           <t>张三</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>5200</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -458,11 +530,73 @@
           <t>李四</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>技术部</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>行政部</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>